--- a/seed/dishes.xlsx
+++ b/seed/dishes.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1008"/>
+  <dimension ref="A1:I1046"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -32780,6 +32780,1222 @@
         <v>150</v>
       </c>
     </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>Варенье клубничное</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>Варенье</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>варенье клубника</t>
+        </is>
+      </c>
+      <c r="D1009" t="n">
+        <v>271</v>
+      </c>
+      <c r="E1009" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1009" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1009" t="n">
+        <v>68</v>
+      </c>
+      <c r="H1009" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>Варенье малиновое</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>Варенье</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>варенье малина</t>
+        </is>
+      </c>
+      <c r="D1010" t="n">
+        <v>273</v>
+      </c>
+      <c r="E1010" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F1010" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1010" t="n">
+        <v>68</v>
+      </c>
+      <c r="H1010" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>Варенье вишнёвое</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>Варенье</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>варенье вишня</t>
+        </is>
+      </c>
+      <c r="D1011" t="n">
+        <v>275</v>
+      </c>
+      <c r="E1011" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1011" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1011" t="n">
+        <v>70</v>
+      </c>
+      <c r="H1011" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>Варенье абрикосовое</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>Варенье</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>варенье абрикос</t>
+        </is>
+      </c>
+      <c r="D1012" t="n">
+        <v>269</v>
+      </c>
+      <c r="E1012" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1012" t="n">
+        <v>66</v>
+      </c>
+      <c r="H1012" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>Варенье из чёрной смородины</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>Варенье</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>варенье смородина чёрная</t>
+        </is>
+      </c>
+      <c r="D1013" t="n">
+        <v>284</v>
+      </c>
+      <c r="E1013" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F1013" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1013" t="n">
+        <v>71</v>
+      </c>
+      <c r="H1013" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>Варенье яблочное</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>Варенье</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>варенье яблоко</t>
+        </is>
+      </c>
+      <c r="D1014" t="n">
+        <v>265</v>
+      </c>
+      <c r="E1014" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1014" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1014" t="n">
+        <v>66</v>
+      </c>
+      <c r="H1014" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>Варенье сливовое</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>Варенье</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>варенье слива</t>
+        </is>
+      </c>
+      <c r="D1015" t="n">
+        <v>270</v>
+      </c>
+      <c r="E1015" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F1015" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1015" t="n">
+        <v>67</v>
+      </c>
+      <c r="H1015" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>Варенье персиковое</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>Варенье</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>варенье персик</t>
+        </is>
+      </c>
+      <c r="D1016" t="n">
+        <v>267</v>
+      </c>
+      <c r="E1016" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F1016" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1016" t="n">
+        <v>66</v>
+      </c>
+      <c r="H1016" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>Варенье из грецких орехов</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Варенье</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>варенье грецкий орех, зелёный орех</t>
+        </is>
+      </c>
+      <c r="D1017" t="n">
+        <v>320</v>
+      </c>
+      <c r="E1017" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1017" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1017" t="n">
+        <v>55</v>
+      </c>
+      <c r="H1017" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>Варенье из лепестков роз</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>Варенье</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>варенье розовое</t>
+        </is>
+      </c>
+      <c r="D1018" t="n">
+        <v>280</v>
+      </c>
+      <c r="E1018" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1018" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1018" t="n">
+        <v>70</v>
+      </c>
+      <c r="H1018" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>Варенье из крыжовника</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>Варенье</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>варенье крыжовник</t>
+        </is>
+      </c>
+      <c r="D1019" t="n">
+        <v>272</v>
+      </c>
+      <c r="E1019" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1019" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G1019" t="n">
+        <v>67</v>
+      </c>
+      <c r="H1019" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>Джем ягодный</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>Варенье</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>джем, джем ягодный</t>
+        </is>
+      </c>
+      <c r="D1020" t="n">
+        <v>260</v>
+      </c>
+      <c r="E1020" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F1020" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1020" t="n">
+        <v>65</v>
+      </c>
+      <c r="H1020" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>Повидло яблочное</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>Варенье</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>повидло</t>
+        </is>
+      </c>
+      <c r="D1021" t="n">
+        <v>250</v>
+      </c>
+      <c r="E1021" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F1021" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G1021" t="n">
+        <v>62</v>
+      </c>
+      <c r="H1021" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>Конфитюр клубничный</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Варенье</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>конфитюр</t>
+        </is>
+      </c>
+      <c r="D1022" t="n">
+        <v>220</v>
+      </c>
+      <c r="E1022" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1022" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G1022" t="n">
+        <v>55</v>
+      </c>
+      <c r="H1022" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>Грецкий орех</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>Орехи</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>грецкие орехи</t>
+        </is>
+      </c>
+      <c r="D1023" t="n">
+        <v>654</v>
+      </c>
+      <c r="E1023" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F1023" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="G1023" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H1023" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>Миндаль</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>Орехи</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>миндаль орех</t>
+        </is>
+      </c>
+      <c r="D1024" t="n">
+        <v>609</v>
+      </c>
+      <c r="E1024" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F1024" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="G1024" t="n">
+        <v>13</v>
+      </c>
+      <c r="H1024" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>Фундук</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Орехи</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>лесной орех</t>
+        </is>
+      </c>
+      <c r="D1025" t="n">
+        <v>628</v>
+      </c>
+      <c r="E1025" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1025" t="n">
+        <v>61</v>
+      </c>
+      <c r="G1025" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H1025" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>Кешью</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>Орехи</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>орехи кешью</t>
+        </is>
+      </c>
+      <c r="D1026" t="n">
+        <v>553</v>
+      </c>
+      <c r="E1026" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F1026" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="G1026" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="H1026" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>Арахис</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>Орехи</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>арахис жареный</t>
+        </is>
+      </c>
+      <c r="D1027" t="n">
+        <v>567</v>
+      </c>
+      <c r="E1027" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="F1027" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="G1027" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H1027" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>Фисташки</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Орехи</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>фисташки солёные</t>
+        </is>
+      </c>
+      <c r="D1028" t="n">
+        <v>560</v>
+      </c>
+      <c r="E1028" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F1028" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="G1028" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="H1028" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>Кедровые орехи</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Орехи</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>кедровые орешки</t>
+        </is>
+      </c>
+      <c r="D1029" t="n">
+        <v>673</v>
+      </c>
+      <c r="E1029" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F1029" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="G1029" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H1029" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>Бразильский орех</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Орехи</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>бразильский орех</t>
+        </is>
+      </c>
+      <c r="D1030" t="n">
+        <v>656</v>
+      </c>
+      <c r="E1030" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F1030" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="G1030" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H1030" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>Макадамия</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Орехи</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>орех макадамия</t>
+        </is>
+      </c>
+      <c r="D1031" t="n">
+        <v>718</v>
+      </c>
+      <c r="E1031" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F1031" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="G1031" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H1031" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>Пекан</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Орехи</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>орех пекан</t>
+        </is>
+      </c>
+      <c r="D1032" t="n">
+        <v>691</v>
+      </c>
+      <c r="E1032" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F1032" t="n">
+        <v>72</v>
+      </c>
+      <c r="G1032" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H1032" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>Смесь орехов</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Орехи</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>ореховая смесь, ассорти орехов</t>
+        </is>
+      </c>
+      <c r="D1033" t="n">
+        <v>620</v>
+      </c>
+      <c r="E1033" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1033" t="n">
+        <v>55</v>
+      </c>
+      <c r="G1033" t="n">
+        <v>18</v>
+      </c>
+      <c r="H1033" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>Каштаны жареные</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Орехи</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>каштан жареный</t>
+        </is>
+      </c>
+      <c r="D1034" t="n">
+        <v>245</v>
+      </c>
+      <c r="E1034" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F1034" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G1034" t="n">
+        <v>53</v>
+      </c>
+      <c r="H1034" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>Орехи в мёде</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Орехи</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>орехи с мёдом</t>
+        </is>
+      </c>
+      <c r="D1035" t="n">
+        <v>480</v>
+      </c>
+      <c r="E1035" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1035" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1035" t="n">
+        <v>40</v>
+      </c>
+      <c r="H1035" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>Мёд цветочный</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Мёд</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>мед, мед цветочный</t>
+        </is>
+      </c>
+      <c r="D1036" t="n">
+        <v>314</v>
+      </c>
+      <c r="E1036" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1036" t="n">
+        <v>80</v>
+      </c>
+      <c r="H1036" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>Мёд липовый</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Мёд</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>мед липовый</t>
+        </is>
+      </c>
+      <c r="D1037" t="n">
+        <v>315</v>
+      </c>
+      <c r="E1037" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1037" t="n">
+        <v>80</v>
+      </c>
+      <c r="H1037" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>Мёд гречишный</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>Мёд</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>мед гречишный</t>
+        </is>
+      </c>
+      <c r="D1038" t="n">
+        <v>309</v>
+      </c>
+      <c r="E1038" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1038" t="n">
+        <v>79</v>
+      </c>
+      <c r="H1038" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>Мёд акациевый</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Мёд</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>мед акациевый, мед белой акации</t>
+        </is>
+      </c>
+      <c r="D1039" t="n">
+        <v>320</v>
+      </c>
+      <c r="E1039" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1039" t="n">
+        <v>81</v>
+      </c>
+      <c r="H1039" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>Мёд подсолнечный</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Мёд</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>мед подсолнечный</t>
+        </is>
+      </c>
+      <c r="D1040" t="n">
+        <v>312</v>
+      </c>
+      <c r="E1040" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1040" t="n">
+        <v>80</v>
+      </c>
+      <c r="H1040" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>Мёд каштановый</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Мёд</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>мед каштановый</t>
+        </is>
+      </c>
+      <c r="D1041" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1041" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1041" t="n">
+        <v>78</v>
+      </c>
+      <c r="H1041" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>Мёд горный</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Мёд</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>мед горный, мед разнотравье</t>
+        </is>
+      </c>
+      <c r="D1042" t="n">
+        <v>310</v>
+      </c>
+      <c r="E1042" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1042" t="n">
+        <v>79</v>
+      </c>
+      <c r="H1042" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>Мёд майский</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Мёд</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>мед майский</t>
+        </is>
+      </c>
+      <c r="D1043" t="n">
+        <v>315</v>
+      </c>
+      <c r="E1043" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1043" t="n">
+        <v>80</v>
+      </c>
+      <c r="H1043" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>Мёд с прополисом</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>Мёд</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>мед прополис</t>
+        </is>
+      </c>
+      <c r="D1044" t="n">
+        <v>300</v>
+      </c>
+      <c r="E1044" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1044" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G1044" t="n">
+        <v>76</v>
+      </c>
+      <c r="H1044" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>Мёд с орехами</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Мёд</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>мед ореховый, мед с грецким орехом</t>
+        </is>
+      </c>
+      <c r="D1045" t="n">
+        <v>380</v>
+      </c>
+      <c r="E1045" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1045" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1045" t="n">
+        <v>68</v>
+      </c>
+      <c r="H1045" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>Сотовый мёд</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>Мёд</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>мед в сотах, соты</t>
+        </is>
+      </c>
+      <c r="D1046" t="n">
+        <v>320</v>
+      </c>
+      <c r="E1046" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1046" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1046" t="n">
+        <v>78</v>
+      </c>
+      <c r="H1046" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I308"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
